--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_27_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_27_R3.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.681100000000001</v>
+        <v>8.578900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.046</v>
+        <v>5.8847</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6351</v>
+        <v>2.6942</v>
       </c>
       <c r="G2" t="n">
         <v>4.4753</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9222</v>
+        <v>1.82</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8259</v>
+        <v>0.6647</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0964</v>
+        <v>1.1554</v>
       </c>
       <c r="V2" t="n">
         <v>1.3558</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8814</v>
+        <v>5.2205</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1906</v>
+        <v>4.0674</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6908</v>
+        <v>1.1531</v>
       </c>
       <c r="G3" t="n">
         <v>2.557</v>
@@ -688,13 +688,13 @@
         <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8938</v>
+        <v>2.233</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3343</v>
+        <v>1.2111</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5595</v>
+        <v>1.0218</v>
       </c>
       <c r="V3" t="n">
         <v>2.2862</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2769</v>
+        <v>3.4587</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3097</v>
+        <v>2.5587</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="n">
         <v>2.9172</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0403</v>
+        <v>0.2221</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0499</v>
+        <v>0.2989</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0097</v>
+        <v>-0.0769</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9907</v>
+        <v>3.1757</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5982</v>
+        <v>-1.0517</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5889</v>
+        <v>4.2274</v>
       </c>
       <c r="G5" t="n">
         <v>3.1107</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9423</v>
+        <v>0.2427</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8883</v>
+        <v>-0.3418</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.054</v>
+        <v>0.5845</v>
       </c>
       <c r="V5" t="n">
         <v>1.214</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1405</v>
+        <v>2.1924</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5599</v>
+        <v>0.4584</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7004</v>
+        <v>1.734</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1236</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3984</v>
+        <v>0.6535</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8215</v>
+        <v>0.1968</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4231</v>
+        <v>0.4567</v>
       </c>
       <c r="V6" t="n">
         <v>2.8223</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.611</v>
+        <v>0.7289</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3029</v>
+        <v>-0.1849</v>
       </c>
       <c r="F7" t="n">
         <v>0.9137999999999999</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1494</v>
+        <v>0.2673</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U7" t="n">
         <v>0.2908</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.409</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="E8" t="n">
         <v>-0.923</v>
       </c>
       <c r="F8" t="n">
-        <v>1.332</v>
+        <v>1.6009</v>
       </c>
       <c r="G8" t="n">
         <v>2.3946</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1046</v>
+        <v>0.3734</v>
       </c>
       <c r="T8" t="n">
         <v>0.1142</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0097</v>
+        <v>0.2592</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9304</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>F. NTILIKINA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2626</v>
+        <v>0.3523</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0282</v>
+        <v>0.9865</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7657</v>
+        <v>-0.6342</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7882</v>
+        <v>-0.0039</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9182</v>
+        <v>-2.3026</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7065</v>
+        <v>2.2987</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1298</v>
+        <v>0.6218</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-1.7338</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5018</v>
+        <v>2.3555</v>
       </c>
       <c r="M9" t="n">
-        <v>0.918</v>
+        <v>-0.6256</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2866</v>
+        <v>-0.5688</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2046</v>
+        <v>-0.0568</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7921</v>
+        <v>0.2634</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1221</v>
+        <v>0.4523</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6699000000000001</v>
+        <v>-0.1889</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.5387</v>
+        <v>0.7886</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7501</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. NTILIKINA</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7422</v>
+        <v>-0.238</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1608</v>
+        <v>-0.8356</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.903</v>
+        <v>0.5976</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0039</v>
+        <v>0.7882</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.3026</v>
+        <v>-0.9182</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2987</v>
+        <v>1.7065</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6218</v>
+        <v>-0.1298</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7338</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>2.3555</v>
+        <v>0.5018</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6256</v>
+        <v>0.918</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5688</v>
+        <v>-0.2866</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0568</v>
+        <v>1.2046</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8312</v>
+        <v>0.8167</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>0.3148</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4577</v>
+        <v>0.5019</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7886</v>
+        <v>-2.5387</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2836</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4148</v>
+        <v>-0.792</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7494</v>
+        <v>-3.3955</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3346</v>
+        <v>2.6035</v>
       </c>
       <c r="G11" t="n">
         <v>1.1739</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5913</v>
+        <v>0.0314</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.3418</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4574</v>
+        <v>-1.0871</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0636</v>
+        <v>-0.8277</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3938</v>
+        <v>-0.2593</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2429</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1423</v>
+        <v>0.228</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.007</v>
+        <v>0.1415</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0973</v>
+        <v>-2.8785</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.228</v>
+        <v>-2.1101</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8693</v>
+        <v>-0.7685</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4766</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1568</v>
+        <v>0.0619</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0668</v>
+        <v>0.0512</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0163</v>
+        <v>19.3897</v>
       </c>
       <c r="E14" t="n">
-        <v>4.253899999999998</v>
+        <v>4.627199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>14.7624</v>
+        <v>14.7625</v>
       </c>
       <c r="G14" t="n">
         <v>17.6372</v>
@@ -1522,7 +1522,7 @@
         <v>9.509399999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7962</v>
+        <v>5.796200000000001</v>
       </c>
       <c r="L14" t="n">
         <v>3.713100000000001</v>
@@ -1537,7 +1537,7 @@
         <v>8.3657</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.958600000000001</v>
+        <v>-6.9586</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2367</v>
@@ -1546,19 +1546,19 @@
         <v>9.278099999999998</v>
       </c>
       <c r="S14" t="n">
-        <v>6.840100000000001</v>
+        <v>7.213399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.341299999999999</v>
+        <v>2.7148</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4984</v>
+        <v>4.4986</v>
       </c>
       <c r="V14" t="n">
-        <v>1.497599999999999</v>
+        <v>1.4976</v>
       </c>
       <c r="W14" t="n">
-        <v>8.639800000000001</v>
+        <v>8.639799999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-7.142200000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6642</v>
+        <v>1.7098</v>
       </c>
       <c r="E15" t="n">
-        <v>1.87</v>
+        <v>0.9264</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7942</v>
+        <v>0.7834</v>
       </c>
       <c r="G15" t="n">
         <v>0.4488</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2876</v>
+        <v>0.3332</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2819</v>
+        <v>0.3383</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0057</v>
+        <v>-0.005</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4605</v>
+        <v>0.7357</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0043</v>
+        <v>0.1222</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4563</v>
+        <v>0.6135</v>
       </c>
       <c r="G16" t="n">
         <v>1.115</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.4874</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7231</v>
+        <v>-0.6051</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0395</v>
+        <v>0.1177</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8197</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1025</v>
+        <v>-0.0689</v>
       </c>
       <c r="E17" t="n">
         <v>-0.7992</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6967</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>-1.5943</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2763</v>
+        <v>-0.2427</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>S. SANLI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3067</v>
+        <v>-0.9352</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3115</v>
+        <v>-0.3212</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6182</v>
+        <v>-0.614</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3723</v>
+        <v>-0.5301</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1836</v>
+        <v>-0.162</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5559</v>
+        <v>-0.368</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1176</v>
+        <v>0.0168</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5952</v>
+        <v>0.0168</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7127</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2547</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4116</v>
+        <v>-0.1788</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8431</v>
+        <v>-0.368</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9058</v>
+        <v>-0.0314</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7512</v>
+        <v>-0.1061</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1546</v>
+        <v>0.0747</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SANLI</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0532</v>
+        <v>-1.2045</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4392</v>
+        <v>-0.9986</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.614</v>
+        <v>-0.206</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5301</v>
+        <v>-1.91</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.162</v>
+        <v>-2.5559</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.368</v>
+        <v>0.6459</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0168</v>
+        <v>-1.3878</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>-1.4614</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.5222</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1788</v>
+        <v>-1.0945</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.368</v>
+        <v>0.5723</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3195</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1494</v>
+        <v>-1.1527</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>-1.0414</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0747</v>
+        <v>-0.1114</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>0.9304</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8165</v>
+        <v>-1.5192</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3524</v>
+        <v>0.3679</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4641</v>
+        <v>-1.887</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.91</v>
+        <v>-1.3723</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5559</v>
+        <v>0.1836</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6459</v>
+        <v>-1.5559</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3878</v>
+        <v>-0.1176</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4614</v>
+        <v>0.5952</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>-0.7127</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5222</v>
+        <v>-1.2547</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0945</v>
+        <v>-0.4116</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5723</v>
+        <v>-0.8431</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7647</v>
+        <v>-0.3066</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3952</v>
+        <v>-0.1924</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3694</v>
+        <v>-0.1142</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9304</v>
+        <v>-0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8223</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8919</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1119</v>
+        <v>-1.5228</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0348</v>
+        <v>-1.6809</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0771</v>
+        <v>0.1581</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0501</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7576</v>
+        <v>-1.1685</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0297</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7279</v>
+        <v>-0.4927</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3471</v>
+        <v>-1.5328</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6962</v>
+        <v>-1.1064</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6509</v>
+        <v>-0.4264</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5467</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7282</v>
+        <v>-0.914</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0218</v>
+        <v>-0.4321</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7064</v>
+        <v>-0.4819</v>
       </c>
       <c r="V22" t="n">
         <v>0.5361</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. DANGUBIC</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8008</v>
+        <v>-2.7651</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2531</v>
+        <v>-3.0267</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5477</v>
+        <v>0.2615</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9764</v>
+        <v>-3.1906</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1897</v>
+        <v>-0.6877</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7867</v>
+        <v>-2.5029</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7541</v>
+        <v>-2.5434</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9677</v>
+        <v>-0.0973</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7863</v>
+        <v>-2.4461</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2223</v>
+        <v>-0.6472</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.222</v>
+        <v>-0.5904</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0004</v>
+        <v>-0.0568</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6959</v>
+        <v>2.5515</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0158</v>
+        <v>-0.912</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1968</v>
+        <v>-0.4832</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.181</v>
+        <v>-0.4288</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>N. DANGUBIC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6402</v>
+        <v>-2.8795</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4985</v>
+        <v>-1.489</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1417</v>
+        <v>-1.3905</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1906</v>
+        <v>-2.9764</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6877</v>
+        <v>-1.1897</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5029</v>
+        <v>-1.7867</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.5434</v>
+        <v>-1.7541</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0973</v>
+        <v>-0.9677</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.4461</v>
+        <v>-0.7863</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6472</v>
+        <v>-1.2223</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5904</v>
+        <v>-0.222</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0568</v>
+        <v>-1.0004</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7871</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.955</v>
+        <v>-0.0391</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.832</v>
+        <v>-0.0237</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.9622</v>
+        <v>-8.2475</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.8749</v>
+        <v>-6.757</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0872</v>
+        <v>-1.4905</v>
       </c>
       <c r="G25" t="n">
         <v>-4.0308</v>
@@ -2404,13 +2404,13 @@
         <v>2.5515</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8232</v>
+        <v>-1.1086</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0807</v>
+        <v>-0.9627</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2574</v>
+        <v>-0.1458</v>
       </c>
       <c r="V25" t="n">
         <v>-0.7886</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-19.0164</v>
+        <v>-18.23</v>
       </c>
       <c r="E26" t="n">
         <v>-14.7625</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.2537</v>
+        <v>-3.4676</v>
       </c>
       <c r="G26" t="n">
         <v>-17.6375</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.5584</v>
+        <v>-5.558399999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-12.0791</v>
@@ -2461,7 +2461,7 @@
         <v>0.2379</v>
       </c>
       <c r="L26" t="n">
-        <v>-8.3659</v>
+        <v>-8.365899999999998</v>
       </c>
       <c r="M26" t="n">
         <v>-9.5093</v>
@@ -2482,13 +2482,13 @@
         <v>16.2368</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.8399</v>
+        <v>-6.053500000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.4983</v>
+        <v>-4.4984</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.3414</v>
+        <v>-1.5551</v>
       </c>
       <c r="V26" t="n">
         <v>-1.4976</v>
